--- a/content/xls/indicators_01.01.2025.xlsx
+++ b/content/xls/indicators_01.01.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4597F015-7F88-4953-94F7-1156E6B73DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D143619F-FC28-49CC-9B6D-2D68B5FEFD3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5329" yWindow="1280" windowWidth="23631" windowHeight="12542" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3089" yWindow="5625" windowWidth="23631" windowHeight="8566" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -39,12 +39,6 @@
     <t>Уровень финансовой доступности</t>
   </si>
   <si>
-    <t>Присутствие банков</t>
-  </si>
-  <si>
-    <t>Присутствие Отделений почтовой связи</t>
-  </si>
-  <si>
     <t>↑</t>
   </si>
   <si>
@@ -55,24 +49,6 @@
  дистанционного банковского обслуживания</t>
   </si>
   <si>
-    <t>Присутствие банкоматов</t>
-  </si>
-  <si>
-    <t>Присутствие торговых точек с сервисом «Выдача наличных на кассе»</t>
-  </si>
-  <si>
-    <t>Присутствие точек финансового доступа</t>
-  </si>
-  <si>
-    <t>Присутствие финансовых помощников</t>
-  </si>
-  <si>
-    <t>77.9%</t>
-  </si>
-  <si>
-    <t>22.1%</t>
-  </si>
-  <si>
     <t>536 ед.</t>
   </si>
   <si>
@@ -91,7 +67,31 @@
     <t>Без динамики (начальная точка)</t>
   </si>
   <si>
-    <t>221 ед.</t>
+    <t>Количество банков</t>
+  </si>
+  <si>
+    <t>Количество Отделений почтовой связи</t>
+  </si>
+  <si>
+    <t>Количество банкоматов</t>
+  </si>
+  <si>
+    <t>Количество торговых точек с сервисом «Выдача наличных на кассе»</t>
+  </si>
+  <si>
+    <t>Количество точек финансового доступа</t>
+  </si>
+  <si>
+    <t>Количество финансовых помощников</t>
+  </si>
+  <si>
+    <t>77.8%</t>
+  </si>
+  <si>
+    <t>22.2%</t>
+  </si>
+  <si>
+    <t>217 ед.</t>
   </si>
 </sst>
 </file>
@@ -505,25 +505,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -533,64 +533,64 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/content/xls/indicators_01.01.2025.xlsx
+++ b/content/xls/indicators_01.01.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D143619F-FC28-49CC-9B6D-2D68B5FEFD3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C05C07-6A59-4CB0-AB9B-B4F9F2B15E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3089" yWindow="5625" windowWidth="23631" windowHeight="8566" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -85,13 +85,14 @@
     <t>Количество финансовых помощников</t>
   </si>
   <si>
-    <t>77.8%</t>
-  </si>
-  <si>
     <t>22.2%</t>
   </si>
   <si>
     <t>217 ед.</t>
+  </si>
+  <si>
+    <t>77.8%
+Выше среднего</t>
   </si>
 </sst>
 </file>
@@ -185,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -206,6 +207,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -531,15 +535,15 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:13" ht="29.55" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>18</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>4</v>
